--- a/Friday, 17 July 2026 - Friday, 24 July 2026.xlsx
+++ b/Friday, 17 July 2026 - Friday, 24 July 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akum1255\Desktop\Current Task Progress\Leaning Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B69A79-7ABF-4F0E-9FD7-CAD6632B0D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767BD71C-ADAD-4DE2-8C6B-02455262DE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="791" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="144">
   <si>
     <t xml:space="preserve">Topic </t>
   </si>
@@ -533,15 +533,6 @@
     <t>Angular Part4</t>
   </si>
   <si>
-    <t>Testing Part3</t>
-  </si>
-  <si>
-    <t>Docker Part4</t>
-  </si>
-  <si>
-    <t>Jenkins Part3</t>
-  </si>
-  <si>
     <t>Schema</t>
   </si>
   <si>
@@ -582,6 +573,24 @@
   </si>
   <si>
     <t>✅Section 8:Spring Boot REST API Development Basics</t>
+  </si>
+  <si>
+    <t>Testing Part4</t>
+  </si>
+  <si>
+    <t>Docker Part5</t>
+  </si>
+  <si>
+    <t>Jenkins Part6</t>
+  </si>
+  <si>
+    <t>Testing Part7</t>
+  </si>
+  <si>
+    <t>AWS Part8</t>
+  </si>
+  <si>
+    <t>Final Test Part8</t>
   </si>
 </sst>
 </file>
@@ -2269,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F5CCDB0-BC81-4945-8026-509DC19E37BE}">
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.90625" customWidth="1"/>
@@ -2398,7 +2407,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B9" s="33" t="s">
         <v>7</v>
@@ -2492,7 +2501,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B15" s="33" t="s">
         <v>7</v>
@@ -2646,7 +2655,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="14" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="B26" s="34"/>
       <c r="C26" s="35"/>
@@ -2656,7 +2665,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="25" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B27" s="33" t="s">
         <v>7</v>
@@ -2728,7 +2737,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="B32" s="34"/>
       <c r="C32" s="35"/>
@@ -2738,7 +2747,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B33" s="33" t="s">
         <v>7</v>
@@ -2810,7 +2819,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="14" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="B38" s="34"/>
       <c r="C38" s="35"/>
@@ -2820,7 +2829,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B39" s="33" t="s">
         <v>7</v>
@@ -2892,7 +2901,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="14" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B44" s="34"/>
       <c r="C44" s="35"/>
@@ -2902,7 +2911,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B45" s="33" t="s">
         <v>7</v>
@@ -2961,6 +2970,170 @@
         <v>42</v>
       </c>
       <c r="F48" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="36"/>
+      <c r="B49" s="16"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="10"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="15"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="5"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="6"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="36"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="10"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" s="34"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="15"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="5"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="6"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="8" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3005,7 +3178,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B2" s="30" t="s">
         <v>117</v>
@@ -3025,7 +3198,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="22" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B3" s="30" t="s">
         <v>118</v>
@@ -3045,7 +3218,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="22" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B4" s="30" t="s">
         <v>85</v>
@@ -3065,7 +3238,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B5" s="30" t="s">
         <v>87</v>
@@ -3085,7 +3258,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="22" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>22</v>
@@ -3105,7 +3278,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="22" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B7" s="30" t="s">
         <v>27</v>
@@ -3125,7 +3298,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B8" s="30" t="s">
         <v>32</v>
@@ -3145,7 +3318,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="22" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>32</v>
